--- a/research/traditional_assets/database/data/indonesia/indonesia_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.007999999999999997</v>
+        <v>0.09825</v>
       </c>
       <c r="E2">
-        <v>0.0843</v>
+        <v>0.223</v>
       </c>
       <c r="G2">
-        <v>0.01000687002754055</v>
+        <v>-0.006398157330688762</v>
       </c>
       <c r="H2">
-        <v>0.01000687002754055</v>
+        <v>-0.006398157330688762</v>
       </c>
       <c r="I2">
-        <v>0.02287658730878256</v>
+        <v>-0.01046555734805519</v>
       </c>
       <c r="J2">
-        <v>0.01928684148856647</v>
+        <v>-0.01008050436151319</v>
       </c>
       <c r="K2">
-        <v>30.666</v>
+        <v>12.664</v>
       </c>
       <c r="L2">
-        <v>0.03089094788248023</v>
+        <v>0.05787590316845891</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>8.84</v>
       </c>
       <c r="N2">
-        <v>0.004160702992377592</v>
+        <v>0.008878354491402859</v>
       </c>
       <c r="O2">
-        <v>0.1630470227613643</v>
+        <v>0.6980416929879975</v>
       </c>
       <c r="P2">
-        <v>5</v>
+        <v>8.84</v>
       </c>
       <c r="Q2">
-        <v>0.004160702992377592</v>
+        <v>0.008878354491402859</v>
       </c>
       <c r="R2">
-        <v>0.1630470227613643</v>
+        <v>0.6980416929879975</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>277.089</v>
+        <v>209.603</v>
       </c>
       <c r="V2">
-        <v>0.2305770062909829</v>
+        <v>0.210512413626868</v>
       </c>
       <c r="W2">
-        <v>0.01567933032839665</v>
+        <v>0.01214128141047685</v>
       </c>
       <c r="X2">
-        <v>0.04184754863878296</v>
+        <v>0.08080394629468068</v>
       </c>
       <c r="Y2">
-        <v>-0.02616821831038631</v>
+        <v>-0.06866266488420383</v>
       </c>
       <c r="Z2">
-        <v>1.457138705288142</v>
+        <v>0.3663331692633256</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04181518564985447</v>
+        <v>0.08079549385265485</v>
       </c>
       <c r="AC2">
-        <v>-0.0418126732294523</v>
+        <v>-0.08094035104531749</v>
       </c>
       <c r="AD2">
-        <v>158.546</v>
+        <v>168.411</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>158.546</v>
+        <v>168.411</v>
       </c>
       <c r="AG2">
-        <v>-118.543</v>
+        <v>-41.19199999999998</v>
       </c>
       <c r="AH2">
-        <v>0.1165551443614705</v>
+        <v>0.1446716794477408</v>
       </c>
       <c r="AI2">
-        <v>0.1410941995516553</v>
+        <v>0.1839188538366527</v>
       </c>
       <c r="AJ2">
-        <v>-0.1094401007406915</v>
+        <v>-0.04315612139702121</v>
       </c>
       <c r="AK2">
-        <v>-0.1400224427120246</v>
+        <v>-0.05833916366180504</v>
       </c>
       <c r="AL2">
-        <v>0.6820000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="AM2">
-        <v>-4.619999999999999</v>
+        <v>-1.577</v>
       </c>
       <c r="AN2">
-        <v>6.724319280685384</v>
+        <v>-87.25958549222798</v>
       </c>
       <c r="AO2">
-        <v>33.2991202346041</v>
+        <v>-76.33333333333334</v>
       </c>
       <c r="AP2">
-        <v>-5.027695309186529</v>
+        <v>21.34300518134714</v>
       </c>
       <c r="AQ2">
-        <v>-4.915584415584417</v>
+        <v>1.452124286620165</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT Panin Sekuritas Tbk (IDX:PANS)</t>
+          <t>PT Yulie Sekuritas Indonesia Tbk (IDX:YULE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +722,106 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0308</v>
-      </c>
-      <c r="E3">
-        <v>-0.0529</v>
+        <v>1.069</v>
       </c>
       <c r="G3">
-        <v>0.2561538461538462</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.2561538461538462</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.5923076923076923</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.5248361204013378</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>19.8</v>
+        <v>1.69</v>
       </c>
       <c r="L3">
-        <v>0.5076923076923077</v>
+        <v>0.528125</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.07836990595611286</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.2525252525252525</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>5</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.07836990595611286</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.2525252525252525</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0.965</v>
+        <v>3.05</v>
       </c>
       <c r="V3">
-        <v>0.01512539184952978</v>
+        <v>0.01400367309458218</v>
       </c>
       <c r="W3">
-        <v>0.2551546391752578</v>
+        <v>0.05671140939597315</v>
       </c>
       <c r="X3">
-        <v>0.04365241439199483</v>
+        <v>0.08078943863564109</v>
       </c>
       <c r="Y3">
-        <v>0.2115022247832629</v>
+        <v>-0.02407802923966793</v>
       </c>
       <c r="Z3">
-        <v>0.461320085166785</v>
+        <v>0.1871345029239766</v>
       </c>
       <c r="AA3">
-        <v>0.2421174437621502</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04222031799954729</v>
+        <v>0.08078943863564109</v>
       </c>
       <c r="AC3">
-        <v>0.1998971257626029</v>
+        <v>-0.08078943863564109</v>
       </c>
       <c r="AD3">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>5.795</v>
+        <v>-3.05</v>
       </c>
       <c r="AH3">
-        <v>0.09580498866213151</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.06459010128033632</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.08326747611178964</v>
+        <v>-0.01420256111757858</v>
       </c>
       <c r="AK3">
-        <v>0.05588504749505761</v>
+        <v>-0.1131725417439703</v>
       </c>
       <c r="AL3">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.521</v>
-      </c>
-      <c r="AN3">
-        <v>0.2864406779661017</v>
-      </c>
-      <c r="AO3">
-        <v>36.96</v>
-      </c>
-      <c r="AP3">
-        <v>0.2455508474576271</v>
+        <v>-0.19</v>
       </c>
       <c r="AQ3">
-        <v>44.33781190019194</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -855,23 +840,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="G4">
-        <v>-0</v>
-      </c>
-      <c r="H4">
-        <v>-0</v>
-      </c>
-      <c r="I4">
-        <v>-0</v>
-      </c>
-      <c r="J4">
-        <v>-0</v>
-      </c>
       <c r="K4">
-        <v>-5.22</v>
-      </c>
-      <c r="L4">
-        <v>1.231132075471698</v>
+        <v>-6.46</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -895,31 +865,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5.48</v>
+        <v>4.33</v>
       </c>
       <c r="V4">
-        <v>0.02361051271003878</v>
+        <v>0.05682414698162729</v>
       </c>
       <c r="W4">
-        <v>-0.1577039274924471</v>
+        <v>-0.2204778156996587</v>
       </c>
       <c r="X4">
-        <v>0.0418126732294523</v>
+        <v>0.08078943863564109</v>
       </c>
       <c r="Y4">
-        <v>-0.1995166007218994</v>
+        <v>-0.3012672543352998</v>
       </c>
       <c r="Z4">
-        <v>-0.1775544388609715</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0418126732294523</v>
+        <v>0.08078943863564109</v>
       </c>
       <c r="AC4">
-        <v>-0.0418126732294523</v>
+        <v>-0.08078943863564109</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -931,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-5.48</v>
+        <v>-4.33</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -940,16 +910,16 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.02418144912187804</v>
+        <v>-0.06024766940308891</v>
       </c>
       <c r="AK4">
-        <v>-0.2300587741393787</v>
+        <v>-0.259748050389922</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.967</v>
+        <v>-0.331</v>
       </c>
       <c r="AQ4">
         <v>-0</v>
@@ -963,7 +933,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT Yulie Sekuritas Indonesia Tbk (IDX:YULE)</t>
+          <t>PT Reliance Sekuritas Indonesia Tbk (IDX:RELI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,7 +942,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>1.672</v>
+        <v>0.199</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -987,58 +957,61 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>9.52</v>
+        <v>1.7</v>
       </c>
       <c r="L5">
-        <v>0.9333333333333333</v>
+        <v>0.4427083333333333</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>1.8</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.02313624678663239</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>1.8</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.02313624678663239</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>12.7</v>
+        <v>2.69</v>
       </c>
       <c r="V5">
-        <v>0.08017676767676767</v>
+        <v>0.03457583547557841</v>
       </c>
       <c r="W5">
-        <v>0.4882051282051282</v>
+        <v>0.04871060171919771</v>
       </c>
       <c r="X5">
-        <v>0.0418126732294523</v>
+        <v>0.08078943863564109</v>
       </c>
       <c r="Y5">
-        <v>0.4463924549756759</v>
+        <v>-0.03207883691644338</v>
       </c>
       <c r="Z5">
-        <v>0.613349368610944</v>
+        <v>0.1466768525592055</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0418126732294523</v>
+        <v>0.08078943863564109</v>
       </c>
       <c r="AC5">
-        <v>-0.0418126732294523</v>
+        <v>-0.08078943863564109</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1050,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-12.7</v>
+        <v>-2.69</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1059,19 +1032,16 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.08716540837336992</v>
+        <v>-0.03581413926241513</v>
       </c>
       <c r="AK5">
-        <v>-0.7426900584795321</v>
+        <v>-0.08816781383153063</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.212</v>
-      </c>
-      <c r="AQ5">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1052,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT Reliance Sekuritas Indonesia Tbk (IDX:RELI)</t>
+          <t>PT Himalaya Energi Perkasa Tbk (IDX:HADE)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1090,9 +1060,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D6">
-        <v>-0.184</v>
-      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1106,10 +1073,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>-0.067</v>
+        <v>-0.006</v>
       </c>
       <c r="L6">
-        <v>-0.02607003891050584</v>
+        <v>-0.02362204724409449</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1133,31 +1100,31 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>8.720000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="V6">
-        <v>0.1559928443649374</v>
+        <v>0.01563421828908555</v>
       </c>
       <c r="W6">
-        <v>-0.001953352769679301</v>
+        <v>-0.01023890784982935</v>
       </c>
       <c r="X6">
-        <v>0.0418126732294523</v>
+        <v>0.08078943863564109</v>
       </c>
       <c r="Y6">
-        <v>-0.0437660259991316</v>
+        <v>-0.09102834648547044</v>
       </c>
       <c r="Z6">
-        <v>0.1159485675614708</v>
+        <v>0.4941634241245136</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.0418126732294523</v>
+        <v>0.08078943863564109</v>
       </c>
       <c r="AC6">
-        <v>-0.0418126732294523</v>
+        <v>-0.08078943863564109</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1169,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-8.720000000000001</v>
+        <v>-0.106</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1178,19 +1145,16 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.1848240779991522</v>
+        <v>-0.01588252921786035</v>
       </c>
       <c r="AK6">
-        <v>-0.3330786860198625</v>
+        <v>-0.1387434554973822</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1.63</v>
-      </c>
-      <c r="AQ6">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1210,10 +1174,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.605</v>
-      </c>
-      <c r="E7">
-        <v>0.187</v>
+        <v>-0.462</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1228,10 +1189,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>16.6</v>
+        <v>-22.6</v>
       </c>
       <c r="L7">
-        <v>1276.923076923077</v>
+        <v>-1614.285714285714</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1240,7 +1201,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1249,37 +1210,37 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.622</v>
+        <v>5.14</v>
       </c>
       <c r="V7">
-        <v>0.03064039408866995</v>
+        <v>0.3835820895522388</v>
       </c>
       <c r="W7">
-        <v>0.2448377581120944</v>
+        <v>-0.255656108597285</v>
       </c>
       <c r="X7">
-        <v>0.0418126732294523</v>
+        <v>0.08078943863564109</v>
       </c>
       <c r="Y7">
-        <v>0.2030250848826421</v>
+        <v>-0.3364455472329261</v>
       </c>
       <c r="Z7">
-        <v>0.0001924671325358285</v>
+        <v>0.0001594932671056529</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.0418126732294523</v>
+        <v>0.08078943863564109</v>
       </c>
       <c r="AC7">
-        <v>-0.0418126732294523</v>
+        <v>-0.08078943863564109</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1291,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-0.622</v>
+        <v>-5.14</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1300,16 +1261,16 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.03160890334383575</v>
+        <v>-0.6222760290556899</v>
       </c>
       <c r="AK7">
-        <v>-0.007086058009979721</v>
+        <v>-0.08615487763995977</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.101</v>
+        <v>-0.031</v>
       </c>
       <c r="AQ7">
         <v>-0</v>
@@ -1323,7 +1284,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PT Himalaya Energi Perkasa Tbk (IDX:HADE)</t>
+          <t>PT Minna Padi Investama Sekuritas Tbk (IDX:PADI)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1331,26 +1292,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D8">
-        <v>-0.227</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
       <c r="K8">
-        <v>-0.07099999999999999</v>
-      </c>
-      <c r="L8">
-        <v>-0.2679245283018867</v>
+        <v>-1.83</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1374,55 +1317,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.07199999999999999</v>
+        <v>0.224</v>
       </c>
       <c r="V8">
-        <v>0.009703504043126684</v>
+        <v>0.006187845303867403</v>
       </c>
       <c r="W8">
-        <v>-0.1165845648604269</v>
+        <v>-0.1057803468208093</v>
       </c>
       <c r="X8">
-        <v>0.0418126732294523</v>
+        <v>0.08152692164902617</v>
       </c>
       <c r="Y8">
-        <v>-0.1583972380898792</v>
+        <v>-0.1873072684698354</v>
       </c>
       <c r="Z8">
-        <v>0.489833641404806</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.0418126732294523</v>
+        <v>0.08109126345499389</v>
       </c>
       <c r="AC8">
-        <v>-0.0418126732294523</v>
+        <v>-0.08109126345499389</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>0.748</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>0.748</v>
       </c>
       <c r="AG8">
-        <v>-0.07199999999999999</v>
+        <v>0.524</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.02024466818231027</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>0.04905561385099685</v>
       </c>
       <c r="AJ8">
-        <v>-0.00979858464888405</v>
+        <v>0.01426859819191809</v>
       </c>
       <c r="AK8">
-        <v>-0.08266360505166474</v>
+        <v>0.03487752928647497</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1439,7 +1382,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PT Minna Padi Investama Sekuritas Tbk (IDX:PADI)</t>
+          <t>PT Panin Sekuritas Tbk (IDX:PANS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1447,101 +1390,113 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.07440000000000001</v>
+      </c>
+      <c r="E9">
+        <v>0.156</v>
+      </c>
       <c r="G9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>-2.39</v>
+        <v>18.8</v>
       </c>
       <c r="L9">
-        <v>1.912</v>
+        <v>0.5164835164835165</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>7.04</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.08018223234624146</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>0.374468085106383</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>7.04</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.08018223234624146</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>0.374468085106383</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>0.41</v>
+        <v>0.833</v>
       </c>
       <c r="V9">
-        <v>0.01035353535353535</v>
+        <v>0.0094874715261959</v>
       </c>
       <c r="W9">
-        <v>-0.127807486631016</v>
+        <v>0.1958333333333333</v>
       </c>
       <c r="X9">
-        <v>0.04220948459377617</v>
+        <v>0.08202114477694056</v>
       </c>
       <c r="Y9">
-        <v>-0.1700169712247922</v>
+        <v>0.1138121885563928</v>
       </c>
       <c r="Z9">
-        <v>-0.06448617416425918</v>
+        <v>0.3575814136254236</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04190774108415867</v>
+        <v>0.08150511825895908</v>
       </c>
       <c r="AC9">
-        <v>-0.04190774108415867</v>
+        <v>-0.08150511825895908</v>
       </c>
       <c r="AD9">
-        <v>0.905</v>
+        <v>3.03</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.905</v>
+        <v>3.03</v>
       </c>
       <c r="AG9">
-        <v>0.4950000000000001</v>
+        <v>2.197</v>
       </c>
       <c r="AH9">
-        <v>0.02234292062708308</v>
+        <v>0.03335902234944402</v>
       </c>
       <c r="AI9">
-        <v>0.0497116176874485</v>
+        <v>0.02825701762566446</v>
       </c>
       <c r="AJ9">
-        <v>0.01234567901234568</v>
+        <v>0.02441192484193918</v>
       </c>
       <c r="AK9">
-        <v>0.02781680247260467</v>
+        <v>0.0206490784514601</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>-0.062</v>
+      </c>
+      <c r="AQ9">
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -1552,7 +1507,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PT Kresna Graha Investama Tbk (IDX:KREN)</t>
+          <t>PT Trimegah Sekuritas Indonesia Tbk (IDX:TRIM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1561,7 +1516,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>1.327</v>
+        <v>0.122</v>
+      </c>
+      <c r="E10">
+        <v>0.29</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1576,10 +1534,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>-17.9</v>
+        <v>12.2</v>
       </c>
       <c r="L10">
-        <v>-0.02267257758074731</v>
+        <v>0.2904761904761904</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1588,7 +1546,7 @@
         <v>-0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1597,67 +1555,67 @@
         <v>-0</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>27.8</v>
+        <v>26.1</v>
       </c>
       <c r="V10">
-        <v>0.2273098937040066</v>
+        <v>0.2538910505836576</v>
       </c>
       <c r="W10">
-        <v>-0.2064590542099193</v>
+        <v>0.2</v>
       </c>
       <c r="X10">
-        <v>0.04382868282804465</v>
+        <v>0.09526721735587744</v>
       </c>
       <c r="Y10">
-        <v>-0.2502877370379639</v>
+        <v>0.1047327826441225</v>
       </c>
       <c r="Z10">
-        <v>9.493975324081868</v>
+        <v>0.7355516637478109</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04246132844906109</v>
+        <v>0.08791273792362643</v>
       </c>
       <c r="AC10">
-        <v>-0.04246132844906109</v>
+        <v>-0.08791273792362643</v>
       </c>
       <c r="AD10">
-        <v>14.2</v>
+        <v>41.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>14.2</v>
+        <v>41.7</v>
       </c>
       <c r="AG10">
-        <v>-13.6</v>
+        <v>15.6</v>
       </c>
       <c r="AH10">
-        <v>0.104029304029304</v>
+        <v>0.2885813148788928</v>
       </c>
       <c r="AI10">
-        <v>0.06896551724137931</v>
+        <v>0.375</v>
       </c>
       <c r="AJ10">
-        <v>-0.125114995400184</v>
+        <v>0.1317567567567568</v>
       </c>
       <c r="AK10">
-        <v>-0.07636159460976981</v>
+        <v>0.1833137485311399</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-0.904</v>
+        <v>-0.891</v>
       </c>
       <c r="AQ10">
         <v>-0</v>
@@ -1671,7 +1629,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PT Trimegah Sekuritas Indonesia Tbk (IDX:TRIM)</t>
+          <t>PT MNC Kapital Indonesia Tbk (IDX:BCAP)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1680,10 +1638,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.04679999999999999</v>
-      </c>
-      <c r="E11">
-        <v>0.0843</v>
+        <v>0.0745</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1698,10 +1653,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>4.6</v>
+        <v>12.3</v>
       </c>
       <c r="L11">
-        <v>0.1580756013745704</v>
+        <v>0.09283018867924529</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1725,64 +1680,61 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>36.4</v>
+        <v>163.7</v>
       </c>
       <c r="V11">
-        <v>0.203125</v>
+        <v>0.7674636661978433</v>
       </c>
       <c r="W11">
-        <v>0.08214285714285714</v>
+        <v>0.03452147067078305</v>
       </c>
       <c r="X11">
-        <v>0.04496169790563634</v>
+        <v>0.1013372942605272</v>
       </c>
       <c r="Y11">
-        <v>0.0371811592372208</v>
+        <v>-0.06681582358974419</v>
       </c>
       <c r="Z11">
-        <v>0.3839050131926122</v>
+        <v>0.517376024990238</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.04276991298474962</v>
+        <v>0.09331747010006797</v>
       </c>
       <c r="AC11">
-        <v>-0.04276991298474962</v>
+        <v>-0.09331747010006797</v>
       </c>
       <c r="AD11">
-        <v>32.5</v>
+        <v>122.8</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>32.5</v>
+        <v>122.8</v>
       </c>
       <c r="AG11">
-        <v>-3.899999999999999</v>
+        <v>-40.89999999999999</v>
       </c>
       <c r="AH11">
-        <v>0.1535191308455361</v>
+        <v>0.3653674501636417</v>
       </c>
       <c r="AI11">
-        <v>0.3475935828877005</v>
+        <v>0.2359269932756964</v>
       </c>
       <c r="AJ11">
-        <v>-0.02224757558471192</v>
+        <v>-0.2372389791183294</v>
       </c>
       <c r="AK11">
-        <v>-0.06830122591943956</v>
+        <v>-0.1146300448430493</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1.25</v>
-      </c>
-      <c r="AQ11">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1793,7 +1745,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PT MNC Kapital Indonesia Tbk (IDX:BCAP)</t>
+          <t>PT Surya Fajar Capital Tbk (IDX:SFAN)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1801,26 +1753,23 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D12">
-        <v>0.105</v>
-      </c>
       <c r="G12">
-        <v>0</v>
+        <v>-2.314049586776859</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>-2.314049586776859</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>-3.785123966942149</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>-3.785123966942149</v>
       </c>
       <c r="K12">
-        <v>4.87</v>
+        <v>-3.13</v>
       </c>
       <c r="L12">
-        <v>0.03874303898170246</v>
+        <v>-5.173553719008265</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1829,7 +1778,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1838,192 +1787,79 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>178.2</v>
+        <v>3.43</v>
       </c>
       <c r="V12">
-        <v>0.9748358862144418</v>
+        <v>0.02096577017114915</v>
       </c>
       <c r="W12">
-        <v>0.01567933032839665</v>
+        <v>-0.2100671140939597</v>
       </c>
       <c r="X12">
-        <v>0.05168160313399858</v>
+        <v>0.08081845395372028</v>
       </c>
       <c r="Y12">
-        <v>-0.03600227280560193</v>
+        <v>-0.29088556804768</v>
       </c>
       <c r="Z12">
-        <v>0.4560957910014514</v>
+        <v>0.06630863656291099</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>-0.2509864094695308</v>
       </c>
       <c r="AB12">
-        <v>0.04335466340133477</v>
+        <v>0.0808015490696686</v>
       </c>
       <c r="AC12">
-        <v>-0.04335466340133477</v>
+        <v>-0.3317879585391994</v>
       </c>
       <c r="AD12">
-        <v>103.9</v>
+        <v>0.133</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>103.9</v>
+        <v>0.133</v>
       </c>
       <c r="AG12">
-        <v>-74.29999999999998</v>
+        <v>-3.297</v>
       </c>
       <c r="AH12">
-        <v>0.3623997209626787</v>
+        <v>0.0008122980706393947</v>
       </c>
       <c r="AI12">
-        <v>0.206642800318218</v>
+        <v>0.01143299234935099</v>
       </c>
       <c r="AJ12">
-        <v>-0.6847926267281103</v>
+        <v>-0.02056730067434796</v>
       </c>
       <c r="AK12">
-        <v>-0.2288971041281577</v>
+        <v>-0.4019261245885652</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AM12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PT Surya Fajar Capital Tbk (IDX:SFAN)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="G13">
-        <v>-0.03010752688172043</v>
-      </c>
-      <c r="H13">
-        <v>-0.03010752688172043</v>
-      </c>
-      <c r="I13">
-        <v>-0.2096774193548387</v>
-      </c>
-      <c r="J13">
-        <v>-0.2096774193548387</v>
-      </c>
-      <c r="K13">
-        <v>0.924</v>
-      </c>
-      <c r="L13">
-        <v>0.4967741935483871</v>
-      </c>
-      <c r="M13">
-        <v>-0</v>
-      </c>
-      <c r="N13">
-        <v>-0</v>
-      </c>
-      <c r="O13">
-        <v>-0</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>-0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>5.72</v>
-      </c>
-      <c r="V13">
-        <v>0.04088634739099356</v>
-      </c>
-      <c r="W13">
-        <v>0.07053435114503817</v>
-      </c>
-      <c r="X13">
-        <v>0.04184754863878296</v>
-      </c>
-      <c r="Y13">
-        <v>0.02868680250625521</v>
-      </c>
-      <c r="Z13">
-        <v>0.1545235523801612</v>
-      </c>
-      <c r="AA13">
-        <v>-0.03240009969261444</v>
-      </c>
-      <c r="AB13">
-        <v>0.04181518564985447</v>
-      </c>
-      <c r="AC13">
-        <v>-0.07421528534246891</v>
-      </c>
-      <c r="AD13">
-        <v>0.281</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0.281</v>
-      </c>
-      <c r="AG13">
-        <v>-5.439</v>
-      </c>
-      <c r="AH13">
-        <v>0.002004551258729785</v>
-      </c>
-      <c r="AI13">
-        <v>0.01838884889732348</v>
-      </c>
-      <c r="AJ13">
-        <v>-0.04045039081964287</v>
-      </c>
-      <c r="AK13">
-        <v>-0.5688735487919674</v>
-      </c>
-      <c r="AL13">
-        <v>0.057</v>
-      </c>
-      <c r="AM13">
-        <v>-0.07700000000000001</v>
-      </c>
-      <c r="AN13">
-        <v>-12.77272727272728</v>
-      </c>
-      <c r="AO13">
-        <v>-6.842105263157895</v>
-      </c>
-      <c r="AP13">
-        <v>247.2272727272727</v>
-      </c>
-      <c r="AQ13">
-        <v>5.064935064935065</v>
+        <v>-0.07199999999999999</v>
+      </c>
+      <c r="AN12">
+        <v>-0.0689119170984456</v>
+      </c>
+      <c r="AO12">
+        <v>-76.33333333333334</v>
+      </c>
+      <c r="AP12">
+        <v>1.708290155440415</v>
+      </c>
+      <c r="AQ12">
+        <v>31.80555555555556</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/indonesia/indonesia_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_brokerage_investment_banking.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09825</v>
+        <v>0.11725</v>
       </c>
       <c r="E2">
-        <v>0.223</v>
+        <v>0.09575</v>
       </c>
       <c r="G2">
-        <v>-0.006398157330688762</v>
+        <v>-0.002672078299991397</v>
       </c>
       <c r="H2">
-        <v>-0.006398157330688762</v>
+        <v>-0.002672078299991397</v>
       </c>
       <c r="I2">
-        <v>-0.01046555734805519</v>
+        <v>-0.004448403078962951</v>
       </c>
       <c r="J2">
-        <v>-0.01008050436151319</v>
+        <v>-0.00399052214579002</v>
       </c>
       <c r="K2">
-        <v>12.664</v>
+        <v>21.53</v>
       </c>
       <c r="L2">
-        <v>0.05787590316845891</v>
+        <v>0.108958041285634</v>
       </c>
       <c r="M2">
-        <v>8.84</v>
+        <v>12.984</v>
       </c>
       <c r="N2">
-        <v>0.008878354491402859</v>
+        <v>0.01481462887551901</v>
       </c>
       <c r="O2">
-        <v>0.6980416929879975</v>
+        <v>0.6030654900139341</v>
       </c>
       <c r="P2">
-        <v>8.84</v>
+        <v>12.604</v>
       </c>
       <c r="Q2">
-        <v>0.008878354491402859</v>
+        <v>0.014381052244843</v>
       </c>
       <c r="R2">
-        <v>0.6980416929879975</v>
+        <v>0.5854156990246169</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.3800000000000008</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.02926678989525576</v>
       </c>
       <c r="U2">
-        <v>209.603</v>
+        <v>253.381</v>
       </c>
       <c r="V2">
-        <v>0.210512413626868</v>
+        <v>0.2891054743613587</v>
       </c>
       <c r="W2">
-        <v>0.01214128141047685</v>
+        <v>0.02237962962962963</v>
       </c>
       <c r="X2">
-        <v>0.08080394629468068</v>
+        <v>0.06741032404280906</v>
       </c>
       <c r="Y2">
-        <v>-0.06866266488420383</v>
+        <v>-0.04503069441317943</v>
       </c>
       <c r="Z2">
-        <v>0.3663331692633256</v>
+        <v>0.3175117621349239</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08079549385265485</v>
+        <v>0.06739628311956516</v>
       </c>
       <c r="AC2">
-        <v>-0.08094035104531749</v>
+        <v>-0.0677480127103819</v>
       </c>
       <c r="AD2">
-        <v>168.411</v>
+        <v>206.032</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>168.411</v>
+        <v>206.032</v>
       </c>
       <c r="AG2">
-        <v>-41.19199999999998</v>
+        <v>-47.34899999999999</v>
       </c>
       <c r="AH2">
-        <v>0.1446716794477408</v>
+        <v>0.1903362978688417</v>
       </c>
       <c r="AI2">
-        <v>0.1839188538366527</v>
+        <v>0.2153004699300173</v>
       </c>
       <c r="AJ2">
-        <v>-0.04315612139702121</v>
+        <v>-0.05711015315734751</v>
       </c>
       <c r="AK2">
-        <v>-0.05833916366180504</v>
+        <v>-0.06729820771209687</v>
       </c>
       <c r="AL2">
-        <v>0.03</v>
+        <v>0.013</v>
       </c>
       <c r="AM2">
-        <v>-1.577</v>
+        <v>-0.079</v>
       </c>
       <c r="AN2">
-        <v>-87.25958549222798</v>
+        <v>-345.6912751677852</v>
       </c>
       <c r="AO2">
-        <v>-76.33333333333334</v>
+        <v>-67.61538461538461</v>
       </c>
       <c r="AP2">
-        <v>21.34300518134714</v>
+        <v>79.4446308724832</v>
       </c>
       <c r="AQ2">
-        <v>1.452124286620165</v>
+        <v>11.12658227848101</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT Yulie Sekuritas Indonesia Tbk (IDX:YULE)</t>
+          <t>PT Lenox Pasifik Investama Tbk (IDX:LPPS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,8 +721,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D3">
-        <v>1.069</v>
+      <c r="E3">
+        <v>-0.05889999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,10 +737,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="L3">
-        <v>0.528125</v>
+        <v>0.9882352941176471</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.05</v>
+        <v>3.41</v>
       </c>
       <c r="V3">
-        <v>0.01400367309458218</v>
+        <v>0.3128440366972477</v>
       </c>
       <c r="W3">
-        <v>0.05671140939597315</v>
+        <v>0.02592592592592593</v>
       </c>
       <c r="X3">
-        <v>0.08078943863564109</v>
+        <v>0.06738876688188276</v>
       </c>
       <c r="Y3">
-        <v>-0.02407802923966793</v>
+        <v>-0.04146284095595684</v>
       </c>
       <c r="Z3">
-        <v>0.1871345029239766</v>
+        <v>0.02849480388870265</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.08078943863564109</v>
+        <v>0.06738876688188276</v>
       </c>
       <c r="AC3">
-        <v>-0.08078943863564109</v>
+        <v>-0.06738876688188276</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-3.05</v>
+        <v>-3.41</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,19 +809,16 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.01420256111757858</v>
+        <v>-0.4552736982643525</v>
       </c>
       <c r="AK3">
-        <v>-0.1131725417439703</v>
+        <v>-0.05492027701723304</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.19</v>
-      </c>
-      <c r="AQ3">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +838,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>-6.46</v>
+        <v>-4.69</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -865,19 +862,19 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>4.33</v>
+        <v>4.95</v>
       </c>
       <c r="V4">
-        <v>0.05682414698162729</v>
+        <v>0.15814696485623</v>
       </c>
       <c r="W4">
-        <v>-0.2204778156996587</v>
+        <v>-0.2233333333333334</v>
       </c>
       <c r="X4">
-        <v>0.08078943863564109</v>
+        <v>0.06738876688188276</v>
       </c>
       <c r="Y4">
-        <v>-0.3012672543352998</v>
+        <v>-0.2907221002152161</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -886,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.08078943863564109</v>
+        <v>0.06738876688188276</v>
       </c>
       <c r="AC4">
-        <v>-0.08078943863564109</v>
+        <v>-0.06738876688188276</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -901,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-4.33</v>
+        <v>-4.95</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -910,19 +907,16 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.06024766940308891</v>
+        <v>-0.1878557874762808</v>
       </c>
       <c r="AK4">
-        <v>-0.259748050389922</v>
+        <v>-0.4479638009049773</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.331</v>
-      </c>
-      <c r="AQ4">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -933,7 +927,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT Reliance Sekuritas Indonesia Tbk (IDX:RELI)</t>
+          <t>PT Himalaya Energi Perkasa Tbk (IDX:HADE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -942,7 +936,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.199</v>
+        <v>0.0547</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -957,61 +951,58 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>1.7</v>
+        <v>-0.022</v>
       </c>
       <c r="L5">
-        <v>0.4427083333333333</v>
+        <v>-0.08494208494208494</v>
       </c>
       <c r="M5">
-        <v>1.8</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.02313624678663239</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>1.058823529411765</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.8</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.02313624678663239</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>1.058823529411765</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>2.69</v>
+        <v>0.028</v>
       </c>
       <c r="V5">
-        <v>0.03457583547557841</v>
+        <v>0.05081669691470054</v>
       </c>
       <c r="W5">
-        <v>0.04871060171919771</v>
+        <v>-0.04044117647058823</v>
       </c>
       <c r="X5">
-        <v>0.08078943863564109</v>
+        <v>0.06738876688188276</v>
       </c>
       <c r="Y5">
-        <v>-0.03207883691644338</v>
+        <v>-0.107829943352471</v>
       </c>
       <c r="Z5">
-        <v>0.1466768525592055</v>
+        <v>0.591324200913242</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08078943863564109</v>
+        <v>0.06738876688188276</v>
       </c>
       <c r="AC5">
-        <v>-0.08078943863564109</v>
+        <v>-0.06738876688188276</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1023,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-2.69</v>
+        <v>-0.028</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1032,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.03581413926241513</v>
+        <v>-0.05353728489483747</v>
       </c>
       <c r="AK5">
-        <v>-0.08816781383153063</v>
+        <v>-0.03539823008849558</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1052,7 +1043,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT Himalaya Energi Perkasa Tbk (IDX:HADE)</t>
+          <t>PT Yulie Sekuritas Indonesia Tbk (IDX:YULE)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1060,6 +1051,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D6">
+        <v>1.053</v>
+      </c>
+      <c r="E6">
+        <v>0.239</v>
+      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1073,10 +1070,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>-0.006</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L6">
-        <v>-0.02362204724409449</v>
+        <v>0.2511111111111111</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1085,7 +1082,7 @@
         <v>-0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1094,61 +1091,61 @@
         <v>-0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.106</v>
+        <v>1.35</v>
       </c>
       <c r="V6">
-        <v>0.01563421828908555</v>
+        <v>0.005705832628909552</v>
       </c>
       <c r="W6">
-        <v>-0.01023890784982935</v>
+        <v>0.01883333333333333</v>
       </c>
       <c r="X6">
-        <v>0.08078943863564109</v>
+        <v>0.06739819175008557</v>
       </c>
       <c r="Y6">
-        <v>-0.09102834648547044</v>
+        <v>-0.04856485841675225</v>
       </c>
       <c r="Z6">
-        <v>0.4941634241245136</v>
+        <v>0.08348794063079777</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08078943863564109</v>
+        <v>0.06739139625922985</v>
       </c>
       <c r="AC6">
-        <v>-0.08078943863564109</v>
+        <v>-0.06739139625922985</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG6">
-        <v>-0.106</v>
+        <v>-1.25</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.0004224757076468104</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.003278688524590164</v>
       </c>
       <c r="AJ6">
-        <v>-0.01588252921786035</v>
+        <v>-0.005311238580837051</v>
       </c>
       <c r="AK6">
-        <v>-0.1387434554973822</v>
+        <v>-0.04288164665523157</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1165,7 +1162,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PT Lenox Pasifik Investama Tbk (IDX:LPPS)</t>
+          <t>PT Reliance Sekuritas Indonesia Tbk (IDX:RELI)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1174,7 +1171,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.462</v>
+        <v>0.338</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1189,91 +1186,91 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-22.6</v>
+        <v>2.64</v>
       </c>
       <c r="L7">
-        <v>-1614.285714285714</v>
+        <v>0.5488565488565489</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>1.1</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.01566951566951567</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>1.1</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.01566951566951567</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>5.14</v>
+        <v>4.83</v>
       </c>
       <c r="V7">
-        <v>0.3835820895522388</v>
+        <v>0.06880341880341879</v>
       </c>
       <c r="W7">
-        <v>-0.255656108597285</v>
+        <v>0.07951807228915662</v>
       </c>
       <c r="X7">
-        <v>0.08078943863564109</v>
+        <v>0.0673989317767741</v>
       </c>
       <c r="Y7">
-        <v>-0.3364455472329261</v>
+        <v>0.01211914051238253</v>
       </c>
       <c r="Z7">
-        <v>0.0001594932671056529</v>
+        <v>0.1576532284496886</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.08078943863564109</v>
+        <v>0.06739461671269749</v>
       </c>
       <c r="AC7">
-        <v>-0.08078943863564109</v>
+        <v>-0.06739461671269749</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="AG7">
-        <v>-5.14</v>
+        <v>-4.798</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.0004556327599954437</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.0008115236356258877</v>
       </c>
       <c r="AJ7">
-        <v>-0.6222760290556899</v>
+        <v>-0.07336167089691446</v>
       </c>
       <c r="AK7">
-        <v>-0.08615487763995977</v>
+        <v>-0.1386625050575112</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.031</v>
-      </c>
-      <c r="AQ7">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1284,7 +1281,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PT Minna Padi Investama Sekuritas Tbk (IDX:PADI)</t>
+          <t>PT Panin Sekuritas Tbk (IDX:PANS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1292,86 +1289,113 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D8">
+        <v>0.0322</v>
+      </c>
+      <c r="E8">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
       <c r="K8">
-        <v>-1.83</v>
+        <v>8.609999999999999</v>
+      </c>
+      <c r="L8">
+        <v>0.3389763779527559</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>11.88</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.1590361445783132</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.379790940766551</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>11.5</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.1539491298527443</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.335656213704994</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>0.3800000000000008</v>
+      </c>
+      <c r="T8">
+        <v>0.03198653198653205</v>
       </c>
       <c r="U8">
-        <v>0.224</v>
+        <v>1.41</v>
       </c>
       <c r="V8">
-        <v>0.006187845303867403</v>
+        <v>0.01887550200803213</v>
       </c>
       <c r="W8">
-        <v>-0.1057803468208093</v>
+        <v>0.08457760314341846</v>
       </c>
       <c r="X8">
-        <v>0.08152692164902617</v>
+        <v>0.06869925758545629</v>
       </c>
       <c r="Y8">
-        <v>-0.1873072684698354</v>
+        <v>0.01587834555796216</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>0.2442378145523428</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.08109126345499389</v>
+        <v>0.06810140870806632</v>
       </c>
       <c r="AC8">
-        <v>-0.08109126345499389</v>
+        <v>-0.06810140870806632</v>
       </c>
       <c r="AD8">
-        <v>0.748</v>
+        <v>4.39</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.748</v>
+        <v>4.39</v>
       </c>
       <c r="AG8">
-        <v>0.524</v>
+        <v>2.98</v>
       </c>
       <c r="AH8">
-        <v>0.02024466818231027</v>
+        <v>0.05550638513086357</v>
       </c>
       <c r="AI8">
-        <v>0.04905561385099685</v>
+        <v>0.0419333269653262</v>
       </c>
       <c r="AJ8">
-        <v>0.01426859819191809</v>
+        <v>0.03836251287332646</v>
       </c>
       <c r="AK8">
-        <v>0.03487752928647497</v>
+        <v>0.02885360185902401</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>-0.081</v>
+      </c>
+      <c r="AQ8">
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -1382,7 +1406,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PT Panin Sekuritas Tbk (IDX:PANS)</t>
+          <t>PT Minna Padi Investama Sekuritas Tbk (IDX:PADI)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1390,113 +1414,86 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.07440000000000001</v>
-      </c>
-      <c r="E9">
-        <v>0.156</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
       <c r="K9">
-        <v>18.8</v>
-      </c>
-      <c r="L9">
-        <v>0.5164835164835165</v>
+        <v>-2.53</v>
       </c>
       <c r="M9">
-        <v>7.04</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.08018223234624146</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.374468085106383</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>7.04</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.08018223234624146</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.374468085106383</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>0.833</v>
+        <v>0.493</v>
       </c>
       <c r="V9">
-        <v>0.0094874715261959</v>
+        <v>0.08384353741496599</v>
       </c>
       <c r="W9">
-        <v>0.1958333333333333</v>
+        <v>-0.1744827586206897</v>
       </c>
       <c r="X9">
-        <v>0.08202114477694056</v>
+        <v>0.06987657304482864</v>
       </c>
       <c r="Y9">
-        <v>0.1138121885563928</v>
+        <v>-0.2443593316655183</v>
       </c>
       <c r="Z9">
-        <v>0.3575814136254236</v>
+        <v>0</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.08150511825895908</v>
+        <v>0.06846842647406101</v>
       </c>
       <c r="AC9">
-        <v>-0.08150511825895908</v>
+        <v>-0.06846842647406101</v>
       </c>
       <c r="AD9">
-        <v>3.03</v>
+        <v>0.656</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>3.03</v>
+        <v>0.656</v>
       </c>
       <c r="AG9">
-        <v>2.197</v>
+        <v>0.163</v>
       </c>
       <c r="AH9">
-        <v>0.03335902234944402</v>
+        <v>0.1003671970624235</v>
       </c>
       <c r="AI9">
-        <v>0.02825701762566446</v>
+        <v>0.0539651201052978</v>
       </c>
       <c r="AJ9">
-        <v>0.02441192484193918</v>
+        <v>0.02697335760383916</v>
       </c>
       <c r="AK9">
-        <v>0.0206490784514601</v>
+        <v>0.01397582097230558</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-0.062</v>
-      </c>
-      <c r="AQ9">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1516,10 +1513,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.122</v>
+        <v>0.0795</v>
       </c>
       <c r="E10">
-        <v>0.29</v>
+        <v>0.0968</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1534,91 +1531,91 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>12.2</v>
+        <v>6.21</v>
       </c>
       <c r="L10">
-        <v>0.2904761904761904</v>
+        <v>0.1651595744680851</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>2.943340691685063e-05</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.0006441223832528181</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>2.943340691685063e-05</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.0006441223832528181</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>26.1</v>
+        <v>15.3</v>
       </c>
       <c r="V10">
-        <v>0.2538910505836576</v>
+        <v>0.1125827814569536</v>
       </c>
       <c r="W10">
-        <v>0.2</v>
+        <v>0.08935251798561152</v>
       </c>
       <c r="X10">
-        <v>0.09526721735587744</v>
+        <v>0.07490388909003862</v>
       </c>
       <c r="Y10">
-        <v>0.1047327826441225</v>
+        <v>0.0144486288955729</v>
       </c>
       <c r="Z10">
-        <v>0.7355516637478109</v>
+        <v>0.4418331374853114</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.08791273792362643</v>
+        <v>0.07010024186851853</v>
       </c>
       <c r="AC10">
-        <v>-0.08791273792362643</v>
+        <v>-0.07010024186851853</v>
       </c>
       <c r="AD10">
-        <v>41.7</v>
+        <v>45.8</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>41.7</v>
+        <v>45.8</v>
       </c>
       <c r="AG10">
-        <v>15.6</v>
+        <v>30.5</v>
       </c>
       <c r="AH10">
-        <v>0.2885813148788928</v>
+        <v>0.252063841496973</v>
       </c>
       <c r="AI10">
-        <v>0.375</v>
+        <v>0.3803986710963455</v>
       </c>
       <c r="AJ10">
-        <v>0.1317567567567568</v>
+        <v>0.1832932692307692</v>
       </c>
       <c r="AK10">
-        <v>0.1833137485311399</v>
+        <v>0.2901998097050428</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-0.891</v>
-      </c>
-      <c r="AQ10">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1638,7 +1635,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0745</v>
+        <v>0.155</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1653,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>12.3</v>
+        <v>9.33</v>
       </c>
       <c r="L11">
-        <v>0.09283018867924529</v>
+        <v>0.07548543689320389</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1680,55 +1677,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>163.7</v>
+        <v>218.2</v>
       </c>
       <c r="V11">
-        <v>0.7674636661978433</v>
+        <v>1.575451263537906</v>
       </c>
       <c r="W11">
-        <v>0.03452147067078305</v>
+        <v>0.02733665397011427</v>
       </c>
       <c r="X11">
-        <v>0.1013372942605272</v>
+        <v>0.09231239192438134</v>
       </c>
       <c r="Y11">
-        <v>-0.06681582358974419</v>
+        <v>-0.06497573795426707</v>
       </c>
       <c r="Z11">
-        <v>0.517376024990238</v>
+        <v>0.4476638898949655</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.09331747010006797</v>
+        <v>0.077192845793433</v>
       </c>
       <c r="AC11">
-        <v>-0.09331747010006797</v>
+        <v>-0.077192845793433</v>
       </c>
       <c r="AD11">
-        <v>122.8</v>
+        <v>154.8</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>122.8</v>
+        <v>154.8</v>
       </c>
       <c r="AG11">
-        <v>-40.89999999999999</v>
+        <v>-63.39999999999998</v>
       </c>
       <c r="AH11">
-        <v>0.3653674501636417</v>
+        <v>0.5277872485509717</v>
       </c>
       <c r="AI11">
-        <v>0.2359269932756964</v>
+        <v>0.2784172661870504</v>
       </c>
       <c r="AJ11">
-        <v>-0.2372389791183294</v>
+        <v>-0.8442077230359515</v>
       </c>
       <c r="AK11">
-        <v>-0.1146300448430493</v>
+        <v>-0.1876850207223208</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1754,22 +1751,22 @@
         </is>
       </c>
       <c r="G12">
-        <v>-2.314049586776859</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="H12">
-        <v>-2.314049586776859</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="I12">
-        <v>-3.785123966942149</v>
+        <v>-0.443939393939394</v>
       </c>
       <c r="J12">
-        <v>-3.785123966942149</v>
+        <v>-0.443939393939394</v>
       </c>
       <c r="K12">
-        <v>-3.13</v>
+        <v>-0.263</v>
       </c>
       <c r="L12">
-        <v>-5.173553719008265</v>
+        <v>-0.1328282828282828</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1793,73 +1790,73 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="V12">
-        <v>0.02096577017114915</v>
+        <v>0.01983711460151251</v>
       </c>
       <c r="W12">
-        <v>-0.2100671140939597</v>
+        <v>-0.0228695652173913</v>
       </c>
       <c r="X12">
-        <v>0.08081845395372028</v>
+        <v>0.06742171630884401</v>
       </c>
       <c r="Y12">
-        <v>-0.29088556804768</v>
+        <v>-0.09029128152623532</v>
       </c>
       <c r="Z12">
-        <v>0.06630863656291099</v>
+        <v>0.2510460251046025</v>
       </c>
       <c r="AA12">
-        <v>-0.2509864094695308</v>
+        <v>-0.1114492202358311</v>
       </c>
       <c r="AB12">
-        <v>0.0808015490696686</v>
+        <v>0.06739794952643284</v>
       </c>
       <c r="AC12">
-        <v>-0.3317879585391994</v>
+        <v>-0.1788471697622639</v>
       </c>
       <c r="AD12">
-        <v>0.133</v>
+        <v>0.254</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.133</v>
+        <v>0.254</v>
       </c>
       <c r="AG12">
-        <v>-3.297</v>
+        <v>-3.156</v>
       </c>
       <c r="AH12">
-        <v>0.0008122980706393947</v>
+        <v>0.001475423167628983</v>
       </c>
       <c r="AI12">
-        <v>0.01143299234935099</v>
+        <v>0.02217565915837262</v>
       </c>
       <c r="AJ12">
-        <v>-0.02056730067434796</v>
+        <v>-0.0187028872137676</v>
       </c>
       <c r="AK12">
-        <v>-0.4019261245885652</v>
+        <v>-0.3923421183490801</v>
       </c>
       <c r="AL12">
-        <v>0.03</v>
+        <v>0.013</v>
       </c>
       <c r="AM12">
-        <v>-0.07199999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="AN12">
-        <v>-0.0689119170984456</v>
+        <v>-0.4261744966442954</v>
       </c>
       <c r="AO12">
-        <v>-76.33333333333334</v>
+        <v>-67.61538461538461</v>
       </c>
       <c r="AP12">
-        <v>1.708290155440415</v>
+        <v>5.295302013422819</v>
       </c>
       <c r="AQ12">
-        <v>31.80555555555556</v>
+        <v>-439.5</v>
       </c>
     </row>
   </sheetData>
